--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>256</v>
+        <v>171</v>
       </c>
       <c r="D2">
-        <v>86</v>
+        <v>240</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>133</v>
+        <v>267</v>
       </c>
       <c r="D3">
-        <v>192</v>
+        <v>142</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D3">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3">
         <v>426</v>
